--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff685281eb5+80197]
-	GetHandleVerifier [0x0x7ff685281f10+80288]
-	(No symbol) [0x0x7ff6850002fa]
-	(No symbol) [0x0x7ff685057cd7]
-	(No symbol) [0x0x7ff685057f9c]
-	(No symbol) [0x0x7ff6850aba87]
-	(No symbol) [0x0x7ff6850803bf]
-	(No symbol) [0x0x7ff6850a87fb]
-	(No symbol) [0x0x7ff685080153]
-	(No symbol) [0x0x7ff685048b02]
-	(No symbol) [0x0x7ff6850498d3]
-	GetHandleVerifier [0x0x7ff68553e83d+2949837]
-	GetHandleVerifier [0x0x7ff685538c6a+2926330]
-	GetHandleVerifier [0x0x7ff6855586c7+3055959]
-	GetHandleVerifier [0x0x7ff68529cfee+191102]
-	GetHandleVerifier [0x0x7ff6852a50af+224063]
-	GetHandleVerifier [0x0x7ff68528af64+117236]
-	GetHandleVerifier [0x0x7ff68528b119+117673]
-	GetHandleVerifier [0x0x7ff6852710a8+11064]
+	GetHandleVerifier [0x0x7ff7597d1eb5+80197]
+	GetHandleVerifier [0x0x7ff7597d1f10+80288]
+	(No symbol) [0x0x7ff7595502fa]
+	(No symbol) [0x0x7ff7595a7cd7]
+	(No symbol) [0x0x7ff7595a7f9c]
+	(No symbol) [0x0x7ff7595fba87]
+	(No symbol) [0x0x7ff7595d03bf]
+	(No symbol) [0x0x7ff7595f87fb]
+	(No symbol) [0x0x7ff7595d0153]
+	(No symbol) [0x0x7ff759598b02]
+	(No symbol) [0x0x7ff7595998d3]
+	GetHandleVerifier [0x0x7ff759a8e83d+2949837]
+	GetHandleVerifier [0x0x7ff759a88c6a+2926330]
+	GetHandleVerifier [0x0x7ff759aa86c7+3055959]
+	GetHandleVerifier [0x0x7ff7597ecfee+191102]
+	GetHandleVerifier [0x0x7ff7597f50af+224063]
+	GetHandleVerifier [0x0x7ff7597daf64+117236]
+	GetHandleVerifier [0x0x7ff7597db119+117673]
+	GetHandleVerifier [0x0x7ff7597c10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1248.0</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
